--- a/data/trans_orig/P15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>23796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47119</t>
+          <t>46588</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65840</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426657</t>
+          <t>427188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449933</t>
+          <t>449980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281624</t>
+          <t>278727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297312</t>
+          <t>296735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714617</t>
+          <t>715901</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743364</t>
+          <t>743499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37629</t>
+          <t>38035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19654</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52394</t>
+          <t>52608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329305</t>
+          <t>328899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350394</t>
+          <t>350471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352211</t>
+          <t>350358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365998</t>
+          <t>366166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686405</t>
+          <t>686191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711872</t>
+          <t>712507</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63071</t>
+          <t>63541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>68250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479318</t>
+          <t>478848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506024</t>
+          <t>505744</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157007</t>
+          <t>157321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165990</t>
+          <t>166020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641584</t>
+          <t>641921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670247</t>
+          <t>670177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68360</t>
+          <t>65963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103921</t>
+          <t>102641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106409</t>
+          <t>106400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150905</t>
+          <t>150832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1134413</t>
+          <t>1135693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1169974</t>
+          <t>1172371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654812</t>
+          <t>655963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681914</t>
+          <t>683055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801715</t>
+          <t>1801788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1846211</t>
+          <t>1846220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31382</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319173</t>
+          <t>319621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337071</t>
+          <t>337613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>517718</t>
+          <t>519339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542596</t>
+          <t>542429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847023</t>
+          <t>845881</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875827</t>
+          <t>875688</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19906</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>39269</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49292</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>79675</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>75616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110725</t>
+          <t>113256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258094</t>
+          <t>258932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278295</t>
+          <t>277986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1169386</t>
+          <t>1169085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1199468</t>
+          <t>1200023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1436235</t>
+          <t>1433704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1472306</t>
+          <t>1471344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>211182</t>
+          <t>213090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>272253</t>
+          <t>270656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151361</t>
+          <t>151060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201265</t>
+          <t>201149</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380318</t>
+          <t>377583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>458723</t>
+          <t>456844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2997937</t>
+          <t>2999534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3059008</t>
+          <t>3057100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3176859</t>
+          <t>3176975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3226763</t>
+          <t>3227064</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6189591</t>
+          <t>6191470</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6267996</t>
+          <t>6270731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47538</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,82 +3383,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17329</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28982</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>51291</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>38699</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>69358</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>5,15%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17329</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9608</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>28862</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>51291</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>36761</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>69224</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389673</t>
+          <t>389717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414714</t>
+          <t>415003</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,82 +3496,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>297125</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>285472</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>304859</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>700374</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>682307</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>712966</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>93,18%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>90,77%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>94,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>297125</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>285592</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>304846</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,82%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>700374</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>682441</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>714904</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23109</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45361</t>
+          <t>44102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38741</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44568</t>
+          <t>45856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74806</t>
+          <t>76549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>373436</t>
+          <t>374695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395688</t>
+          <t>396399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299637</t>
+          <t>299270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321036</t>
+          <t>320187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>682002</t>
+          <t>680259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712240</t>
+          <t>710952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44787</t>
+          <t>45351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76327</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61117</t>
+          <t>60317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97122</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>553088</t>
+          <t>551610</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584628</t>
+          <t>584064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235437</t>
+          <t>234732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>250890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>792422</t>
+          <t>794123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828427</t>
+          <t>829227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77820</t>
+          <t>79419</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115875</t>
+          <t>117409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36752</t>
+          <t>36470</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64466</t>
+          <t>65004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124493</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172013</t>
+          <t>169692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1043134</t>
+          <t>1041600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1081189</t>
+          <t>1079590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702191</t>
+          <t>701653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>729905</t>
+          <t>730187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1753654</t>
+          <t>1755975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1801174</t>
+          <t>1802670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53045</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45373</t>
+          <t>46543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75566</t>
+          <t>74940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>79284</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116940</t>
+          <t>116662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457551</t>
+          <t>457750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>482158</t>
+          <t>481540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>685956</t>
+          <t>686582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716149</t>
+          <t>714979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1155178</t>
+          <t>1155456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192527</t>
+          <t>1192834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74204</t>
+          <t>74304</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112858</t>
+          <t>111955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>96311</t>
+          <t>98893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>137465</t>
+          <t>138439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>229293</t>
+          <t>228924</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248550</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>996493</t>
+          <t>997396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1035147</t>
+          <t>1035047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1238768</t>
+          <t>1237794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1279922</t>
+          <t>1277340</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254285</t>
+          <t>254967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323061</t>
+          <t>323248</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>228344</t>
+          <t>226910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291435</t>
+          <t>289161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>502619</t>
+          <t>502157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>594332</t>
+          <t>595984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3098849</t>
+          <t>3098662</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3167625</t>
+          <t>3166943</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3258690</t>
+          <t>3260964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3321781</t>
+          <t>3323215</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6377703</t>
+          <t>6376051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6469416</t>
+          <t>6469878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58247</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396585</t>
+          <t>396297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415596</t>
+          <t>415115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315964</t>
+          <t>316003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333975</t>
+          <t>334980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717900</t>
+          <t>717927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745930</t>
+          <t>745685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>35178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,47 +6396,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>38946</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>26953</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>53097</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>38946</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>27801</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>52874</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350739</t>
+          <t>351217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366900</t>
+          <t>367703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338273</t>
+          <t>337095</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358880</t>
+          <t>358297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,47 +6509,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>710554</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>696403</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>722547</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>96,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>710554</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>696626</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>721699</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21506</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>42550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>54294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477242</t>
+          <t>479364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500408</t>
+          <t>501086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148372</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161466</t>
+          <t>160920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633142</t>
+          <t>633742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658303</t>
+          <t>659263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45533</t>
+          <t>45342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73762</t>
+          <t>75025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>27892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>53319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78386</t>
+          <t>80397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118033</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1075876</t>
+          <t>1074613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1104105</t>
+          <t>1104296</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>773649</t>
+          <t>772557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>798014</t>
+          <t>797984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857481</t>
+          <t>1857367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897128</t>
+          <t>1895117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55178</t>
+          <t>54787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>29099</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53893</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64974</t>
+          <t>64931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100005</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>565528</t>
+          <t>565919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>590264</t>
+          <t>590207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>684351</t>
+          <t>683154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>709183</t>
+          <t>709145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258945</t>
+          <t>1258632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1293976</t>
+          <t>1294019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43031</t>
+          <t>41384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45723</t>
+          <t>45233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78447</t>
+          <t>78582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71360</t>
+          <t>71816</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112117</t>
+          <t>109092</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244114</t>
+          <t>245761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266557</t>
+          <t>266872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1003578</t>
+          <t>1003443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036302</t>
+          <t>1036792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1257053</t>
+          <t>1260078</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1297810</t>
+          <t>1297354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173441</t>
+          <t>174026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228587</t>
+          <t>228058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164823</t>
+          <t>164826</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220268</t>
+          <t>221883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>351923</t>
+          <t>353188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>429511</t>
+          <t>433723</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3157135</t>
+          <t>3157664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3212281</t>
+          <t>3211696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3311328</t>
+          <t>3309713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3366773</t>
+          <t>3366770</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6487807</t>
+          <t>6483595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6565395</t>
+          <t>6564130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>34218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468343</t>
+          <t>470994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489603</t>
+          <t>489904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416383</t>
+          <t>415943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430114</t>
+          <t>430842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>892672</t>
+          <t>893197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>916516</t>
+          <t>916802</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31219</t>
+          <t>31157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36821</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62354</t>
+          <t>63142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414099</t>
+          <t>414635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436612</t>
+          <t>436563</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351361</t>
+          <t>351423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366018</t>
+          <t>365796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772439</t>
+          <t>771651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797972</t>
+          <t>798484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59823</t>
+          <t>58436</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70629</t>
+          <t>67314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608441</t>
+          <t>609828</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656578</t>
+          <t>656464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148736</t>
+          <t>149294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159245</t>
+          <t>159120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764546</t>
+          <t>767861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817776</t>
+          <t>815334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>51470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85812</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26393</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70531</t>
+          <t>67826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82058</t>
+          <t>81569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142881</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>949007</t>
+          <t>951557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983846</t>
+          <t>983349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>907563</t>
+          <t>910268</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>951701</t>
+          <t>952628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870031</t>
+          <t>1870706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930854</t>
+          <t>1931343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54345</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68192</t>
+          <t>67996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71144</t>
+          <t>71698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112483</t>
+          <t>111919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>420701</t>
+          <t>418234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448119</t>
+          <t>447819</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>773143</t>
+          <t>773339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>802902</t>
+          <t>802509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1203898</t>
+          <t>1204462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245237</t>
+          <t>1244683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26763</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>35690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61586</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44197</t>
+          <t>45481</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79157</t>
+          <t>77074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213744</t>
+          <t>207222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236868</t>
+          <t>236229</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>699785</t>
+          <t>701154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>724390</t>
+          <t>725681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>922721</t>
+          <t>924804</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957681</t>
+          <t>956397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151160</t>
+          <t>157474</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234743</t>
+          <t>233357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>167793</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238465</t>
+          <t>236920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>348897</t>
+          <t>349835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453014</t>
+          <t>455213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3141317</t>
+          <t>3142703</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3224900</t>
+          <t>3218586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3339293</t>
+          <t>3340838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3408720</t>
+          <t>3409965</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6500804</t>
+          <t>6498605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6604921</t>
+          <t>6603983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23576</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46588</t>
+          <t>47453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>26734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>64851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>427188</t>
+          <t>426323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449980</t>
+          <t>450200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278727</t>
+          <t>279946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296735</t>
+          <t>296958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715901</t>
+          <t>715606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>743499</t>
+          <t>742292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38035</t>
+          <t>38388</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52608</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>328899</t>
+          <t>328546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>350471</t>
+          <t>349664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350358</t>
+          <t>350262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366166</t>
+          <t>365709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686191</t>
+          <t>685481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712507</t>
+          <t>711468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68250</t>
+          <t>68736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>478848</t>
+          <t>480363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505744</t>
+          <t>506983</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157321</t>
+          <t>156578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166020</t>
+          <t>165849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641921</t>
+          <t>641435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670177</t>
+          <t>670891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>68065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102641</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31230</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58322</t>
+          <t>57438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106400</t>
+          <t>107360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150832</t>
+          <t>150992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135693</t>
+          <t>1133874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1172371</t>
+          <t>1170269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655963</t>
+          <t>656847</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>683055</t>
+          <t>682936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1801788</t>
+          <t>1801628</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1846220</t>
+          <t>1845260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30934</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>26530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49413</t>
+          <t>49763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>319621</t>
+          <t>320310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337613</t>
+          <t>338166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519339</t>
+          <t>518989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542429</t>
+          <t>542222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845881</t>
+          <t>845882</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875688</t>
+          <t>874678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48737</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79675</t>
+          <t>78984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75616</t>
+          <t>75188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113256</t>
+          <t>112698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258932</t>
+          <t>256904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277986</t>
+          <t>277690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1169085</t>
+          <t>1169776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1200023</t>
+          <t>1199740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1433704</t>
+          <t>1434262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1471344</t>
+          <t>1471772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>213090</t>
+          <t>213880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>270656</t>
+          <t>273587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151060</t>
+          <t>152209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201149</t>
+          <t>202362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>377583</t>
+          <t>378287</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>456844</t>
+          <t>456746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2999534</t>
+          <t>2996603</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3057100</t>
+          <t>3056310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3176975</t>
+          <t>3175762</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3227064</t>
+          <t>3225915</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6191470</t>
+          <t>6191568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6270731</t>
+          <t>6270027</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>48562</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38699</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69358</t>
+          <t>69052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389717</t>
+          <t>388649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415003</t>
+          <t>413734</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285472</t>
+          <t>285480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304859</t>
+          <t>304658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682307</t>
+          <t>682613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712966</t>
+          <t>715027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44102</t>
+          <t>44842</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17824</t>
+          <t>17089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>39500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>45505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>76140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374695</t>
+          <t>373955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396399</t>
+          <t>396544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299270</t>
+          <t>298511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320187</t>
+          <t>320922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680259</t>
+          <t>680668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710952</t>
+          <t>711303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77805</t>
+          <t>78965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25397</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60317</t>
+          <t>59533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95421</t>
+          <t>93411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>551610</t>
+          <t>550450</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>584064</t>
+          <t>582856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234732</t>
+          <t>232816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>250890</t>
+          <t>250433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>794123</t>
+          <t>796133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>829227</t>
+          <t>830011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>78266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117409</t>
+          <t>114464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36470</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65004</t>
+          <t>63498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122997</t>
+          <t>123905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169692</t>
+          <t>172352</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1041600</t>
+          <t>1044545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1079590</t>
+          <t>1080743</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701653</t>
+          <t>703159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>730187</t>
+          <t>729725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1755975</t>
+          <t>1753315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1802670</t>
+          <t>1801762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52846</t>
+          <t>52516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46543</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74940</t>
+          <t>75341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79284</t>
+          <t>80604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116662</t>
+          <t>117522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457750</t>
+          <t>458080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>481540</t>
+          <t>482948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>686582</t>
+          <t>686181</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>714979</t>
+          <t>716059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1155456</t>
+          <t>1154596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192834</t>
+          <t>1191514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>38027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>73475</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111955</t>
+          <t>110096</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98893</t>
+          <t>93797</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138439</t>
+          <t>136010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>228924</t>
+          <t>228855</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247972</t>
+          <t>247548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>997396</t>
+          <t>999255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1035047</t>
+          <t>1035876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1237794</t>
+          <t>1240223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1277340</t>
+          <t>1282436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254967</t>
+          <t>255293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>323248</t>
+          <t>321932</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>226910</t>
+          <t>224440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289161</t>
+          <t>288992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>502157</t>
+          <t>501586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>595984</t>
+          <t>595727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3098662</t>
+          <t>3099978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3166943</t>
+          <t>3166617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3260964</t>
+          <t>3261133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3323215</t>
+          <t>3325685</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6376051</t>
+          <t>6376308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6469878</t>
+          <t>6470449</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>30438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>30005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58220</t>
+          <t>55543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396297</t>
+          <t>395628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415115</t>
+          <t>415738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>316003</t>
+          <t>316617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334980</t>
+          <t>334271</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>717927</t>
+          <t>720604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745685</t>
+          <t>746142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26010</t>
+          <t>26347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35178</t>
+          <t>32662</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351217</t>
+          <t>350880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367703</t>
+          <t>367116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337095</t>
+          <t>339611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358297</t>
+          <t>358919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696403</t>
+          <t>695714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>722547</t>
+          <t>721232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42550</t>
+          <t>45344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54294</t>
+          <t>55052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479364</t>
+          <t>476570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501086</t>
+          <t>499619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148204</t>
+          <t>148571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160920</t>
+          <t>161582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633742</t>
+          <t>632984</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659263</t>
+          <t>658072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45342</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>74955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,49 +7047,49 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>38465</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27978</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53912</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38465</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>27892</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53319</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>94</t>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>80203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118147</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1074613</t>
+          <t>1074683</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1104296</t>
+          <t>1104104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,47 +7160,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>787411</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>771964</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>797898</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>93,47%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>787411</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>772557</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>797984</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857367</t>
+          <t>1856498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895117</t>
+          <t>1895311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>57013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>29085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55090</t>
+          <t>54392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64931</t>
+          <t>64699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>100744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>565919</t>
+          <t>563693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>590207</t>
+          <t>590273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>683852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>709145</t>
+          <t>709159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1258632</t>
+          <t>1258206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1294019</t>
+          <t>1294251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45233</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78582</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>72272</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109092</t>
+          <t>111482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245761</t>
+          <t>245652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266872</t>
+          <t>267307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1004563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1036792</t>
+          <t>1036317</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1260078</t>
+          <t>1257688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1297354</t>
+          <t>1296898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174026</t>
+          <t>173448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228058</t>
+          <t>229794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164826</t>
+          <t>166452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>220950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>353188</t>
+          <t>353557</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433723</t>
+          <t>433584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3157664</t>
+          <t>3155928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3211696</t>
+          <t>3212274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3309713</t>
+          <t>3310646</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3366770</t>
+          <t>3365144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6483595</t>
+          <t>6483734</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6564130</t>
+          <t>6563761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34218</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>52056</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>481376</t>
+          <t>524751</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>470994</t>
+          <t>513233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>489904</t>
+          <t>533242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>424258</t>
+          <t>462223</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415943</t>
+          <t>452983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430842</t>
+          <t>469683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>905634</t>
+          <t>986973</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893197</t>
+          <t>972679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>916802</t>
+          <t>998369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24147</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>39522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31157</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47306</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63142</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>428066</t>
+          <t>457480</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414635</t>
+          <t>443690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436563</t>
+          <t>466080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>359421</t>
+          <t>398160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351423</t>
+          <t>389670</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365796</t>
+          <t>405696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>787487</t>
+          <t>855640</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771651</t>
+          <t>840132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798484</t>
+          <t>867072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33340</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>26772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58436</t>
+          <t>49820</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67314</t>
+          <t>63830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>634924</t>
+          <t>434341</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609828</t>
+          <t>421792</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656464</t>
+          <t>444840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>154912</t>
+          <t>174809</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149294</t>
+          <t>168606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159120</t>
+          <t>179718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>789836</t>
+          <t>609150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767861</t>
+          <t>595279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>815334</t>
+          <t>620947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,67 +9662,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51470</t>
+          <t>58235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83262</t>
+          <t>96774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>55394</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43123</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70817</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>49504</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25466</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67826</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>115993</t>
+          <t>133174</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81569</t>
+          <t>111419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142206</t>
+          <t>159665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -9775,67 +9775,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>968330</t>
+          <t>1054063</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>951557</t>
+          <t>1035069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>983349</t>
+          <t>1073608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>805817</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>790394</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>818088</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>93,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>928590</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>910268</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>952628</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1896919</t>
+          <t>1859880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870706</t>
+          <t>1833389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1931343</t>
+          <t>1881635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,102 +10005,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27227</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56812</t>
+          <t>59770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>56960</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>45259</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>71014</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>97281</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>80104</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>118310</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>53125</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38826</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>67996</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>91434</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>71698</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>111919</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -10118,102 +10118,102 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>436738</t>
+          <t>527643</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418234</t>
+          <t>508194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447819</t>
+          <t>538808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>773890</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>759836</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>785591</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>93,14%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>94,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1301533</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1280504</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1318710</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>93,05%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>94,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>788210</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>773339</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>802509</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1224947</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1204462</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1244683</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46641</t>
+          <t>49198</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35690</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60217</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60420</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77074</t>
+          <t>78940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228778</t>
+          <t>226006</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>207222</t>
+          <t>208152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236229</t>
+          <t>232466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>714730</t>
+          <t>795083</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>701154</t>
+          <t>781498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>725681</t>
+          <t>805594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>943508</t>
+          <t>1021089</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924804</t>
+          <t>1002569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>956397</t>
+          <t>1034067</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>197850</t>
+          <t>218192</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>157474</t>
+          <t>188370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>233357</t>
+          <t>255057</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>207636</t>
+          <t>225412</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167793</t>
+          <t>202406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236920</t>
+          <t>253637</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>405487</t>
+          <t>443604</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349835</t>
+          <t>402264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>455213</t>
+          <t>488531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3178210</t>
+          <t>3224284</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3142703</t>
+          <t>3187419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3218586</t>
+          <t>3254106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3370122</t>
+          <t>3409981</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3340838</t>
+          <t>3381756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3409965</t>
+          <t>3432987</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6548331</t>
+          <t>6634265</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6498605</t>
+          <t>6589338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6603983</t>
+          <t>6675605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
